--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/ARKANSAS_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/ARKANSAS_2012.xlsx
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C114">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C134">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C537">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C749">
